--- a/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente</t>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,66; 90,82</t>
+          <t>56,16; 90,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,46; 81,81</t>
+          <t>47,67; 82,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,43; 81,75</t>
+          <t>56,0; 81,14</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,43; 89,59</t>
+          <t>76,73; 89,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,34; 95,38</t>
+          <t>87,28; 95,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,82; 91,42</t>
+          <t>84,32; 91,34</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,56; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,51; 99,09</t>
+          <t>89,64; 99,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93,57; 99,43</t>
+          <t>93,67; 99,43</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,27; 90,39</t>
+          <t>80,42; 90,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,12; 92,46</t>
+          <t>85,06; 92,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,02; 91,0</t>
+          <t>85,05; 90,96</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>14314</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19305</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33619</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10466; 16851</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13559; 23415</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26362; 38198</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>126206</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>280640</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>114453; 133071</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>146701; 159884</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267510; 289769</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>27726</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39897</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67622</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37144; 41061</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>64785; 68769</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>168247</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>213635</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>381882</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>157227; 176039</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202410; 220819</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>368685; 394305</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,16; 90,42</t>
+          <t>58,67; 91,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,67; 82,32</t>
+          <t>47,79; 82,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,0; 81,14</t>
+          <t>57,63; 81,22</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,73; 89,22</t>
+          <t>77,54; 89,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,28; 95,12</t>
+          <t>87,24; 95,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,32; 91,34</t>
+          <t>84,21; 91,34</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,64; 99,09</t>
+          <t>88,99; 99,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93,67; 99,43</t>
+          <t>93,95; 99,44</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,42; 90,04</t>
+          <t>80,54; 90,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,06; 92,8</t>
+          <t>85,13; 92,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,05; 90,96</t>
+          <t>85,07; 90,66</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10466; 16851</t>
+          <t>10933; 17048</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13559; 23415</t>
+          <t>13592; 23605</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26362; 38198</t>
+          <t>27129; 38240</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>114453; 133071</t>
+          <t>115664; 133376</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146701; 159884</t>
+          <t>146638; 160343</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>267510; 289769</t>
+          <t>267160; 289781</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37144; 41061</t>
+          <t>36879; 41051</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64785; 68769</t>
+          <t>64983; 68778</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157227; 176039</t>
+          <t>157476; 176004</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202410; 220819</t>
+          <t>202587; 220907</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>368685; 394305</t>
+          <t>368776; 392975</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,67; 91,48</t>
+          <t>49,29; 81,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,79; 82,99</t>
+          <t>56,81; 91,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,63; 81,22</t>
+          <t>57,88; 82,29</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,54; 89,42</t>
+          <t>87,02; 95,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,24; 95,4</t>
+          <t>79,42; 89,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,21; 91,34</t>
+          <t>85,32; 91,81</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>88,21; 99,24</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>88,99; 99,06</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93,95; 99,44</t>
+          <t>92,83; 99,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,54; 90,02</t>
+          <t>84,72; 92,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,13; 92,83</t>
+          <t>82,0; 90,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,07; 90,66</t>
+          <t>85,25; 91,16</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>33266</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10933; 17048</t>
+          <t>12934; 21475</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13592; 23605</t>
+          <t>11433; 18337</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27129; 38240</t>
+          <t>26834; 38151</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>143515</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154434</t>
+          <t>124409</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280640</t>
+          <t>267925</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>115664; 133376</t>
+          <t>136264; 149368</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146638; 160343</t>
+          <t>115448; 130783</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>267160; 289781</t>
+          <t>257618; 277212</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>63494</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33487; 37676</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>36879; 41051</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64983; 68778</t>
+          <t>60358; 64716</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>247</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>168247</t>
+          <t>197686</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>157476; 176004</t>
+          <t>187060; 203898</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202587; 220907</t>
+          <t>157881; 174815</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>368776; 392975</t>
+          <t>352379; 376801</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>67,57%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>77,2%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>71,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>49,29; 81,84</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56,81; 91,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57,88; 82,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>87,02; 95,39</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>79,42; 89,97</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>85,32; 91,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>95,99%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>88,21; 99,24</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>92,83; 99,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>84,72; 92,35</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>82,0; 90,79</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>85,25; 91,16</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6756791763892959</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7720026047933717</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7174879196824935</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>17730</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33266</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4929047290785084</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.568104672511728</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5787578076721133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12934; 21475</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11433; 18337</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26834; 38151</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.8184045758241747</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9111897406356824</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.8228616332005936</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9165560560202987</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8558404952738483</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8873260088173697</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>143515</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>124409</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>267925</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8702482495384977</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.7941905594192744</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8531922525935637</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>136264; 149368</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>115448; 130783</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>257618; 277212</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9539357819879525</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8996838394006645</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9180835697030889</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,47 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9598529866695034</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9765574982819769</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>36441</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>27053</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63494</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8820574470608368</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>0.9283252348203558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>33487; 37676</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>60358; 64716</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9924007181605208</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9953536636520192</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8953737853545477</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8673331533679137</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8823115464351646</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>197686</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>166998</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>364684</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8472461812517955</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8199807980237833</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.852541473976632</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>187060; 203898</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>157881; 174815</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>352379; 376801</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9235097441168798</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.90793306823441</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9116282177273293</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>17730</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>15536</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>33266</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>12934</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>11433</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>26834</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>21475</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18337</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>38151</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>209</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>143515</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>124409</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>267925</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>136264</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>115448</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>257618</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>149368</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>130783</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>277212</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>36441</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>27053</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>63494</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>33487</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="n">
+        <v>60358</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>37676</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>64716</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>197686</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>166998</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>364684</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>187060</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>157881</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>352379</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>203898</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>174815</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>376801</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>